--- a/光伏配储项目/电价数据/2026/庆南站.xlsx
+++ b/光伏配储项目/电价数据/2026/庆南站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51049</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.47367</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50707</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45436</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12288</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11158</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12277</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.13099</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16929</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09065000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.00844</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.03284</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17025</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22394</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25978</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10017</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.008919999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.25143</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.18467</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64898</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.53265</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16557</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57452</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46401</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6213099999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.81199</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64334</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63279</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7682599999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.02728</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43595</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67715</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7554299999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.51495</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.64393</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61527</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47384</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42584</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6997000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00651</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69308</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.29022</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7115900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52732</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50522</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50887</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.4997799999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69429</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51546</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05647</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47284</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.57331</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.15276</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5253300000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.80424</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.50927</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12829</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.44564</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49746</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42715</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.59173</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.72257</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.69463</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.6852999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.59058</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.61825</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.54159</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.79372</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.53906</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6563099999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46123</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45454</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46091</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33461</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60324</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.74838</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.6246699999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.47334</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.47252</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4667</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.89808</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6377200000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.66459</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26802</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51637</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48455</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54276</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62212</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.63848</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5981599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47825</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50325</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34243</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45937</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.21239</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.21829</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.22284</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.11797</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.08170999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.23115</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.67576</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06470999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.17127</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24297</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24687</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21698</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13633</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5970299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2987</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.09606999999999999</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.09448000000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.10445</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04443</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04611999999999999</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04684000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04783</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04256</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04239</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04168</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04268</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04205</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04214</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04604999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04479</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21873</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04571</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05168</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05584</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0404</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.20417</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.10484</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.15279</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35092</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7307400000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10368</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00172</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04351</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04407</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33569</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31794</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17256</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17113</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15877</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15647</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220599999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92045</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9162100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8686200000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29956</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8934099999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19292</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8716699999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54567</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33679</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03702</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5367000000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7959700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5304099999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78151</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87739</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87648</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49783</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40596</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21306</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8790800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511699999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62787</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5398500000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42501</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58665</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5960599999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6023200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66822</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5809500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88005</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6332100000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.91915</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86365</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.57857</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35345</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92401</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46694</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4769</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16554</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19919</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19833</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59687</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89036</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.18165</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.01646</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.64563</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.71761</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.59863</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.53896</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47117</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.1042</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.58458</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25201</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.1279</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.58882</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.91047</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.72526</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57625</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32405</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.09238</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19228</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.23522</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.19412</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.16874</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.16866</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18154</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20303</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10474</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.21318</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.17655</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.26296</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34885</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.50592</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24862</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24153</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.23521</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35549</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.04692</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.15909</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22712</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.21794</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.66926</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28691</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34957</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.47271</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.71588</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44571</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.32283</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14496</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20011</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22071</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.46438</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.48838</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.69869</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47603</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48866</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6454099999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16522</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.45895</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.51112</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.50313</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.94421</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.70472</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80863</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5311900000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5426799999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.5195599999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60421</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.56559</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.39881</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51527</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11378</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36545</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22748</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25028</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13993</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17007</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18241</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27876</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22892</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23289</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35017</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17148</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0007199999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11486</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01313</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03929</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01506</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03931</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04782</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02595</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.14084</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03194</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04228</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20331</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.15801</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6050399999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18544</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18235</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66313</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.67803</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.61245</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11041</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19414</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.13887</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14516</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10379</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12863</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04423</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11773</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18574</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02371</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13797</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16184</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.009949999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12081</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12995</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12964</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16309</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25694</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32349</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.03277</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49534</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14113</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31617</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26198</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.53573</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48009</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.51361</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35097</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26598</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24199</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.15553</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17781</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06622</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18279</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03385</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20753</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16859</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07142</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16404</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17744</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15153</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17188</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26115</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34948</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.59866</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27607</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11571</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16933</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03626</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01862</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04552</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16333</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04479</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24703</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.47712</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36919</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47564</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44647</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21509</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11844</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03149</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.00591</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04709000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04722999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04571</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04615</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08101</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02843</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06445000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09961</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17815</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12512</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23914</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12834</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15339</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12094</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24273</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19386</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21173</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3782799999999999</v>
       </c>
     </row>
   </sheetData>
